--- a/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,124 @@
         </is>
       </c>
       <c r="AI2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:43:47</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E3" t="n">
+        <v>154091</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12426</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="I3" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1343</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>715</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>12261</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>9518</v>
+      </c>
+      <c r="R3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4371</v>
+      </c>
+      <c r="T3" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3266</v>
+      </c>
+      <c r="V3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="W3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,6 +830,124 @@
         </is>
       </c>
       <c r="AI3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10:44:56</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E4" t="n">
+        <v>154060</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12425</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="I4" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1341</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>715</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>12256</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9523</v>
+      </c>
+      <c r="R4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4370</v>
+      </c>
+      <c r="T4" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3269</v>
+      </c>
+      <c r="V4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="W4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,124 @@
         </is>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10:46:04</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E5" t="n">
+        <v>154031</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12423</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="I5" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1338</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>715</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>12260</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>9524</v>
+      </c>
+      <c r="R5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4370</v>
+      </c>
+      <c r="T5" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3271</v>
+      </c>
+      <c r="V5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,6 +1066,124 @@
         </is>
       </c>
       <c r="AI5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10:47:14</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>154052</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12421</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I6" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1338</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>716</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>12258</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>9531</v>
+      </c>
+      <c r="R6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4369</v>
+      </c>
+      <c r="T6" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3275</v>
+      </c>
+      <c r="V6" t="n">
+        <v>23</v>
+      </c>
+      <c r="W6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
+++ b/backend/signal_logs/2026-09-01/index_tracker_GOLDM_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,6 +1184,124 @@
         </is>
       </c>
       <c r="AI6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10:48:23</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E7" t="n">
+        <v>154020</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12421</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="I7" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1337</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>716</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>12251</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9528</v>
+      </c>
+      <c r="R7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4367</v>
+      </c>
+      <c r="T7" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3274</v>
+      </c>
+      <c r="V7" t="n">
+        <v>23</v>
+      </c>
+      <c r="W7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>CE writing dominant (bearish)</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
